--- a/DataTables/DetailText/剧情/008_01和尚肾精不足.xlsx
+++ b/DataTables/DetailText/剧情/008_01和尚肾精不足.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C40EBCC-5152-4E87-8237-22D9105E8320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF3264-3A2A-4956-82D1-54B04D209A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -151,19 +140,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/xing_kong/xing_kong.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>性空</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>before</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -364,6 +345,14 @@
   </si>
   <si>
     <t>和尚肾精不足</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/xing_kong/xing_kong_sick.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sick</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -371,11 +360,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -389,7 +378,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -410,7 +399,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -552,7 +541,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -831,27 +820,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -901,12 +890,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -930,7 +919,7 @@
         <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -941,65 +930,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8" ht="18.75">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -1011,20 +1000,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -1050,7 +1039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1058,23 +1047,23 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1082,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>9</v>
@@ -1091,28 +1080,28 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1122,7 +1111,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1132,7 +1121,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1142,7 +1131,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1152,7 +1141,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1162,7 +1151,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>

--- a/DataTables/DetailText/剧情/008_01和尚肾精不足.xlsx
+++ b/DataTables/DetailText/剧情/008_01和尚肾精不足.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF3264-3A2A-4956-82D1-54B04D209A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E1D65E-A20F-41AF-89DA-79E934FB52CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -348,11 +348,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/xing_kong/xing_kong_sick.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/xing_kong/xing_kong_sick.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -890,7 +890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16">
       <c r="A2" s="16" t="s">
         <v>34</v>
       </c>
@@ -919,7 +919,7 @@
         <v>31</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -936,59 +936,59 @@
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" ht="18.75">
+    <row r="20" spans="8:8">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -1053,7 +1053,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
